--- a/results/Int All Data -0.8/Rando_fi_explain.xlsx
+++ b/results/Int All Data -0.8/Rando_fi_explain.xlsx
@@ -1676,466 +1676,466 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.0001977820272319185</v>
+        <v>-0.000538337048717048</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.0004437738405349056</v>
+        <v>-0.0004956955583112276</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0004522855934265114</v>
+        <v>-6.504323158300961e-05</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0001135714803033016</v>
+        <v>0.0007949276397003458</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0002589509576287441</v>
+        <v>-0.0002052546574878555</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0002435413086817694</v>
+        <v>0.002171538186779744</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.000680858669129647</v>
+        <v>-0.0006921266322305254</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0004126681352207539</v>
+        <v>0.0002671103795378305</v>
       </c>
       <c r="J3" t="n">
-        <v>6.030073619770915e-05</v>
+        <v>6.814052692597492e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.0001991195280469149</v>
+        <v>-6.310428253188282e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0001092441463500415</v>
+        <v>3.085324278380598e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>-9.003428170223046e-05</v>
+        <v>-0.0005307038372400419</v>
       </c>
       <c r="N3" t="n">
-        <v>0.002324424377547846</v>
+        <v>0.0001430361177624585</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0007563248518816111</v>
+        <v>0.0005355715822084607</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0004656419234910347</v>
+        <v>0.0003757938216397949</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.004783680025658591</v>
+        <v>0.003930316271819856</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0004745576096438941</v>
+        <v>0.000142740718176434</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.231570612479475e-05</v>
+        <v>-0.0002720836599073074</v>
       </c>
       <c r="T3" t="n">
-        <v>4.734063027926227e-05</v>
+        <v>-0.0001195397100388485</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0006991462447706431</v>
+        <v>0.0006527121331188335</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.001935393561996873</v>
+        <v>-0.0001620481014833496</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0001031464449582753</v>
+        <v>0.0002484752066475571</v>
       </c>
       <c r="X3" t="n">
-        <v>0.001535800669486024</v>
+        <v>0.002496453504711911</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.267085789928958e-05</v>
+        <v>-0.0001859927619880797</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.003507812713163683</v>
+        <v>0.001941290589691584</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.001948660045615369</v>
+        <v>0.002809810217266756</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.0004838835129986451</v>
+        <v>-0.0003492217553428091</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.0002524567612787765</v>
+        <v>-8.089366081612704e-05</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.003030775348914085</v>
+        <v>0.001616206988889613</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.006816384899551611</v>
+        <v>0.007957723842886764</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.0001725409505639841</v>
+        <v>0.0007831527718524967</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.0001770916096685504</v>
+        <v>0.0002758153050047574</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.0007554981003159235</v>
+        <v>-0.0003974689694926592</v>
       </c>
       <c r="AI3" t="n">
-        <v>-5.609899169359614e-05</v>
+        <v>-8.966116129378369e-05</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.0003782266835173686</v>
+        <v>0.004553062760476152</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.01487865375465166</v>
+        <v>0.01388256644858352</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.000225838369807887</v>
+        <v>3.096918150940819e-05</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.003537186046459521</v>
+        <v>0.004193821594131523</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0.0003767604643615563</v>
+        <v>-0.001325079855620568</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.0004234277620757754</v>
+        <v>0.001582284622518273</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0.00149267361723766</v>
+        <v>-0.0006342355284347189</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.002214282386585788</v>
+        <v>0.0005501968277726943</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.005301483333345767</v>
+        <v>0.007580790598050972</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.0008683850839470807</v>
+        <v>-0.0004642621836199378</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.001262336074635492</v>
+        <v>0.001013866728120244</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.000805518675248822</v>
+        <v>0.0001390875956353155</v>
       </c>
       <c r="AV3" t="n">
-        <v>-0.0004727769276966532</v>
+        <v>-0.0001312046274705969</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.0009580010432023946</v>
+        <v>-0.001243467195621548</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0.0002804755755812461</v>
+        <v>0.0003756395677277091</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.00193794401571016</v>
+        <v>0.0007362467171341455</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.0003310617446669507</v>
+        <v>0.0004882022517132822</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.002618168159737323</v>
+        <v>0.001897716456980311</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.004191320645187601</v>
+        <v>0.001593064962901072</v>
       </c>
       <c r="BC3" t="n">
-        <v>-0.0003180840273328888</v>
+        <v>-4.071297932074837e-05</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.0007915262567439407</v>
+        <v>-0.0002290263260999192</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.0005323793773527464</v>
+        <v>-2.79224235583575e-05</v>
       </c>
       <c r="BF3" t="n">
-        <v>7.033295203138778e-05</v>
+        <v>0.00140866385762516</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.0008545940271325761</v>
+        <v>-0.002054559199812644</v>
       </c>
       <c r="BH3" t="n">
-        <v>-8.997488847961363e-05</v>
+        <v>-0.0003105135233610811</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.006140963653294482</v>
+        <v>0.005903365063352315</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.0008213768992734516</v>
+        <v>0.001785891784926207</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.0003695299885176783</v>
+        <v>-0.0007598636560311711</v>
       </c>
       <c r="BL3" t="n">
-        <v>7.67150188731725e-05</v>
+        <v>-0.0005071639191411936</v>
       </c>
       <c r="BM3" t="n">
-        <v>-8.626326181601419e-05</v>
+        <v>0.001489784864376663</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.0019998628599515</v>
+        <v>0.002301930814303973</v>
       </c>
       <c r="BO3" t="n">
-        <v>-0.0006942399283950329</v>
+        <v>-0.0003624333531727652</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.0001912456176879829</v>
+        <v>-9.277993545161346e-05</v>
       </c>
       <c r="BQ3" t="n">
         <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.001749447565549565</v>
+        <v>0.002464977179450181</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.0005238441824141137</v>
+        <v>-1.06449429279021e-05</v>
       </c>
       <c r="BT3" t="n">
-        <v>-0.0003597846693174667</v>
+        <v>0.0002852091877123886</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.0008470110547850139</v>
+        <v>0.0004449970980414474</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0.0001295873033516392</v>
+        <v>-0.0009357479435869899</v>
       </c>
       <c r="BW3" t="n">
-        <v>5.066972353843901e-05</v>
+        <v>7.141678375052972e-05</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.0002409232572362185</v>
+        <v>0.000315945705239613</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.0004777388115293646</v>
+        <v>-0.0008039284262252398</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.0004403667277402557</v>
+        <v>-0.001329314225346387</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.0002450101016968042</v>
+        <v>-0.0001261515025573845</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.0001156382038791426</v>
+        <v>-0.0001106523167052309</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.001089173951354271</v>
+        <v>0.0001792093529554939</v>
       </c>
       <c r="CD3" t="n">
-        <v>-0.000582448059078775</v>
+        <v>-0.0008779507098104277</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0.0003005211704505097</v>
+        <v>-0.0001757215017530811</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.0002818541370113192</v>
+        <v>-0.0001136869588320022</v>
       </c>
       <c r="CG3" t="n">
-        <v>-0.0002927962948016328</v>
+        <v>-0.0003879139695953315</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0.0005700601042384091</v>
+        <v>-0.0006286956331161763</v>
       </c>
       <c r="CI3" t="n">
-        <v>-0.0005114653383434364</v>
+        <v>-0.0008507468427078611</v>
       </c>
       <c r="CJ3" t="n">
-        <v>8.517867143543748e-06</v>
+        <v>9.09439168062298e-06</v>
       </c>
       <c r="CK3" t="n">
-        <v>-0.0006249860779005034</v>
+        <v>0.0004543295481946208</v>
       </c>
       <c r="CL3" t="n">
-        <v>-0.001190889968909517</v>
+        <v>-0.002306700714841208</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.0002962654777173968</v>
+        <v>0.0006636556324982922</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.001192870262438297</v>
+        <v>0.000380833542367739</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.0008875903070074333</v>
+        <v>0.0002255197734192116</v>
       </c>
       <c r="CP3" t="n">
-        <v>-0.0001229897529224499</v>
+        <v>8.726646613332224e-05</v>
       </c>
       <c r="CQ3" t="n">
-        <v>8.095967366840364e-05</v>
+        <v>0.0003901933061296291</v>
       </c>
       <c r="CR3" t="n">
-        <v>-0.001055285647723252</v>
+        <v>-0.001048233954780236</v>
       </c>
       <c r="CS3" t="n">
-        <v>-0.0001109992402781356</v>
+        <v>-0.003278866513938489</v>
       </c>
       <c r="CT3" t="n">
-        <v>-0.001773685945211589</v>
+        <v>-0.003622214599745174</v>
       </c>
       <c r="CU3" t="n">
-        <v>-1.682204419789834e-05</v>
+        <v>-2.300600738884829e-05</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.0002361584489777069</v>
+        <v>-7.425834793151176e-05</v>
       </c>
       <c r="CW3" t="n">
         <v>0</v>
       </c>
       <c r="CX3" t="n">
-        <v>-0.001845116280894209</v>
+        <v>-0.004085850915420886</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.0005411404699705325</v>
+        <v>-0.002368762644681791</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.0001058304724930392</v>
+        <v>0.000132415815206367</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.0002898227988297153</v>
+        <v>0.000188756246423738</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.001252085263025764</v>
+        <v>0.000756941915191266</v>
       </c>
       <c r="DC3" t="n">
-        <v>-0.001894924343962692</v>
+        <v>-0.001392401114849906</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.88075637390617e-05</v>
+        <v>-0.0002196901117329053</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.0002524537277202311</v>
+        <v>0.00117307141363852</v>
       </c>
       <c r="DF3" t="n">
-        <v>-0.0006188354585977162</v>
+        <v>-0.003325599444835751</v>
       </c>
       <c r="DG3" t="n">
-        <v>-0.0001478914652928343</v>
+        <v>-0.0001471491636337363</v>
       </c>
       <c r="DH3" t="n">
-        <v>-0.001084611245981557</v>
+        <v>-0.0008353047063115592</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.00124092500259931</v>
+        <v>-0.001838910313390727</v>
       </c>
       <c r="DJ3" t="n">
-        <v>-0.0009888068283724104</v>
+        <v>-0.001430825382392883</v>
       </c>
       <c r="DK3" t="n">
-        <v>-0.0003636910922537483</v>
+        <v>-0.00068817505364015</v>
       </c>
       <c r="DL3" t="n">
-        <v>-4.780044881971367e-05</v>
+        <v>-2.018343810968437e-05</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.0003449854328821012</v>
+        <v>0.000425292956080664</v>
       </c>
       <c r="DN3" t="n">
-        <v>-0.0007863376205943162</v>
+        <v>-0.0003330010533053384</v>
       </c>
       <c r="DO3" t="n">
-        <v>-0.001468015014273378</v>
+        <v>-0.0009092411339782392</v>
       </c>
       <c r="DP3" t="n">
-        <v>-0.002649842050573648</v>
+        <v>-0.001653999101742944</v>
       </c>
       <c r="DQ3" t="n">
-        <v>-8.16695863716732e-05</v>
+        <v>-4.887979831736278e-05</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.0002876130711856184</v>
+        <v>-0.0001286509475091668</v>
       </c>
       <c r="DS3" t="n">
-        <v>-0.0001364727717490666</v>
+        <v>-0.0001322228204082643</v>
       </c>
       <c r="DT3" t="n">
-        <v>-0.001562145663682788</v>
+        <v>9.738753512695809e-06</v>
       </c>
       <c r="DU3" t="n">
-        <v>-0.001350349067410811</v>
+        <v>-0.0009904618663765263</v>
       </c>
       <c r="DV3" t="n">
-        <v>-2.852184778958655e-06</v>
+        <v>0</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.0001808965219682357</v>
+        <v>-4.306192950980559e-05</v>
       </c>
       <c r="DX3" t="n">
-        <v>-0.001083996080776094</v>
+        <v>-0.0001237801042686071</v>
       </c>
       <c r="DY3" t="n">
-        <v>-0.002491357554987296</v>
+        <v>1.469750471543296e-05</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0.0002940302037107323</v>
+        <v>7.649246755836893e-05</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0.0008328744564509251</v>
+        <v>-0.001068863067852331</v>
       </c>
       <c r="EB3" t="n">
-        <v>-0.001578384901464495</v>
+        <v>-0.002333674524938306</v>
       </c>
       <c r="EC3" t="n">
-        <v>6.085830040414185e-05</v>
+        <v>-6.225233072749251e-05</v>
       </c>
       <c r="ED3" t="n">
-        <v>-4.701413502559705e-05</v>
+        <v>-0.0009028843349493564</v>
       </c>
       <c r="EE3" t="n">
-        <v>5.736461929304659e-05</v>
+        <v>2.914004911194199e-06</v>
       </c>
       <c r="EF3" t="n">
-        <v>-4.258322178716578e-05</v>
+        <v>-0.0005254526769454159</v>
       </c>
       <c r="EG3" t="n">
-        <v>-0.0003650806414399233</v>
+        <v>-0.0001889096066804874</v>
       </c>
       <c r="EH3" t="n">
-        <v>3.85924551840866e-05</v>
+        <v>-0.0002187890199288223</v>
       </c>
       <c r="EI3" t="n">
-        <v>-0.0005935321617560362</v>
+        <v>-0.0007311029702584602</v>
       </c>
       <c r="EJ3" t="n">
-        <v>-0.0005244370768897777</v>
+        <v>-0.0002695544934814708</v>
       </c>
       <c r="EK3" t="n">
-        <v>-0.0001890773530281464</v>
+        <v>1.927848118477348e-05</v>
       </c>
       <c r="EL3" t="n">
-        <v>-2.483445846289345e-05</v>
+        <v>8.540419365999918e-06</v>
       </c>
       <c r="EM3" t="n">
-        <v>7.776813069193533e-05</v>
+        <v>-0.0001173664244386408</v>
       </c>
       <c r="EN3" t="n">
-        <v>3.842391597303374e-05</v>
+        <v>0.0002085750215693083</v>
       </c>
       <c r="EO3" t="n">
         <v>0</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.0001666460214180832</v>
+        <v>8.388332861211767e-05</v>
       </c>
       <c r="EQ3" t="n">
-        <v>-0.0005765433654272535</v>
+        <v>-0.0005512811773323879</v>
       </c>
       <c r="ER3" t="n">
-        <v>1.490626769324765e-05</v>
+        <v>-2.91376216566408e-05</v>
       </c>
       <c r="ES3" t="n">
-        <v>7.444688013934498e-05</v>
+        <v>-6.915350008017685e-05</v>
       </c>
       <c r="ET3" t="n">
-        <v>3.366620030103124e-05</v>
+        <v>-0.0002927325253283142</v>
       </c>
       <c r="EU3" t="n">
-        <v>-5.371756573315121e-05</v>
+        <v>-0.000643879737367874</v>
       </c>
       <c r="EV3" t="n">
-        <v>-4.297039969069382e-05</v>
+        <v>-0.0002205322656185849</v>
       </c>
       <c r="EW3" t="n">
-        <v>-0.0002204491754666449</v>
+        <v>-0.0004643466942238561</v>
       </c>
       <c r="EX3" t="n">
-        <v>-0.0005489774919382427</v>
+        <v>-0.0001230109408799851</v>
       </c>
       <c r="EY3" t="n">
-        <v>-0.0004317918444099578</v>
+        <v>-0.000441354710322619</v>
       </c>
     </row>
     <row r="4">
@@ -2145,466 +2145,466 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002745167551944597</v>
+        <v>0.001994144741456835</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002263481355321707</v>
+        <v>0.001562135994521771</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001158540271268814</v>
+        <v>0.0008489528203585078</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00188558023724631</v>
+        <v>0.001518701236951133</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0008743069625926828</v>
+        <v>0.001077251913575899</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003416716947832871</v>
+        <v>0.005453813234952381</v>
       </c>
       <c r="H4" t="n">
-        <v>0.003130146874482456</v>
+        <v>0.001847270622343833</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001953437525003874</v>
+        <v>0.002291903959154237</v>
       </c>
       <c r="J4" t="n">
-        <v>0.003315877570256538</v>
+        <v>0.002832942275031143</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0008439442541731579</v>
+        <v>0.0004363279607540911</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0005284291143214921</v>
+        <v>0.0004198953054174991</v>
       </c>
       <c r="M4" t="n">
-        <v>0.002362012568974448</v>
+        <v>0.001552442294303519</v>
       </c>
       <c r="N4" t="n">
-        <v>0.006136072325079995</v>
+        <v>0.00504674039937611</v>
       </c>
       <c r="O4" t="n">
-        <v>0.002569145650906482</v>
+        <v>0.00159127917248709</v>
       </c>
       <c r="P4" t="n">
-        <v>0.001327031571738347</v>
+        <v>0.0006961947573191873</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.01019945808614003</v>
+        <v>0.005314559697383874</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001331770901710064</v>
+        <v>0.001478932730447976</v>
       </c>
       <c r="S4" t="n">
-        <v>0.002533481851560918</v>
+        <v>0.002670441671154411</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0006320555275697685</v>
+        <v>0.0007328732323509208</v>
       </c>
       <c r="U4" t="n">
-        <v>0.001630545880538043</v>
+        <v>0.001160989385509211</v>
       </c>
       <c r="V4" t="n">
-        <v>0.006448329001365037</v>
+        <v>0.00212134356608451</v>
       </c>
       <c r="W4" t="n">
-        <v>0.001257558371304565</v>
+        <v>0.002588158766599265</v>
       </c>
       <c r="X4" t="n">
-        <v>0.005671040707838279</v>
+        <v>0.004321756564059332</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0005410870433252548</v>
+        <v>0.0006103702503253972</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.005853060748454333</v>
+        <v>0.006399966226886331</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.003138523353433029</v>
+        <v>0.006580297331745744</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0006026870119137127</v>
+        <v>0.001354172030031371</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.0032274882452136</v>
+        <v>0.001814721518762762</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.005909751999752143</v>
+        <v>0.005622048030633797</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.006807152770159743</v>
+        <v>0.005930001861691552</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.001433961862129075</v>
+        <v>0.002163706467790469</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.0006943433107910901</v>
+        <v>0.001108589635425869</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.001583826046663638</v>
+        <v>0.0008749604755386661</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.001113688568250594</v>
+        <v>0.001258678019385955</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.004804749343751565</v>
+        <v>0.004108854626358174</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.01410694456179172</v>
+        <v>0.01270248425277919</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.001186383717923204</v>
+        <v>0.001178995475147467</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.00895309974820468</v>
+        <v>0.004466193719817374</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.002154151779683144</v>
+        <v>0.001916185883431657</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.002951057718699141</v>
+        <v>0.002012351188074606</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.002286310388622462</v>
+        <v>0.001034100606287255</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.009343734519902948</v>
+        <v>0.002253031525815103</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.004486327064028982</v>
+        <v>0.006759592093050798</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.002393317959878617</v>
+        <v>0.001202006447381366</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.001798096947042739</v>
+        <v>0.004082635437478169</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.001881939958898852</v>
+        <v>0.00203778379476707</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.000984050076832528</v>
+        <v>0.001763601835361968</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.002603078766593857</v>
+        <v>0.00116857723009677</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.0008694290424414718</v>
+        <v>0.0008429498142052767</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.004633461222165466</v>
+        <v>0.003379664349981405</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.002860854221371856</v>
+        <v>0.001764196989895778</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.003773869400706732</v>
+        <v>0.005374173319935809</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.01114028787104244</v>
+        <v>0.004422753502743093</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.0005866025768152737</v>
+        <v>0.000747653326488838</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.001197210609656649</v>
+        <v>0.000826425029778591</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.002057768895608465</v>
+        <v>0.002199289910278564</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.006290185686765314</v>
+        <v>0.005618399740383582</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.004124178683948154</v>
+        <v>0.006262641865296938</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.001261719995222729</v>
+        <v>0.001034991002917079</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.01136831560265281</v>
+        <v>0.007805812431562307</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.001937197248523567</v>
+        <v>0.001731696164079902</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.002945152732437352</v>
+        <v>0.002676752811478068</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.0008650613835464075</v>
+        <v>0.001005119457835619</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.00189487411034888</v>
+        <v>0.0035975631586971</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.006220565905974006</v>
+        <v>0.003888773147046953</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.002813933544158972</v>
+        <v>0.002996729751047322</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.0009743383053791365</v>
+        <v>0.001597887214818128</v>
       </c>
       <c r="BQ4" t="n">
         <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.00486966359060005</v>
+        <v>0.006148633592618877</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.002128645203814935</v>
+        <v>0.001882457436528838</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.00141064009218365</v>
+        <v>0.001615750076265745</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.003498849289759954</v>
+        <v>0.002408750736077017</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.002543832442667647</v>
+        <v>0.004029528465690431</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.0001842871758939114</v>
+        <v>0.0001403704917662838</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.001649516771860287</v>
+        <v>0.002319871006786556</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.003900068909304557</v>
+        <v>0.004586498356988577</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.003241151669367535</v>
+        <v>0.003111796395526497</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.001085694182828722</v>
+        <v>0.0008634411079828637</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.001677824195610548</v>
+        <v>0.002251231254553815</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.002432838981524451</v>
+        <v>0.002116171714552527</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.002432699712140232</v>
+        <v>0.003213373009886776</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.00235614033135326</v>
+        <v>0.00158510000375034</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.002619973216487694</v>
+        <v>0.001573389099349406</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.000949072812154588</v>
+        <v>0.0009575114801799169</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.001471967156382874</v>
+        <v>0.002445929165047727</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.001181433017882819</v>
+        <v>0.001424827440595688</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.0001175093554371357</v>
+        <v>0.000121987857668707</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.001189041191893039</v>
+        <v>0.001334696816299872</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.004201737280268222</v>
+        <v>0.007507611725963894</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.001382143330828396</v>
+        <v>0.001247287099744419</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.001381270047178221</v>
+        <v>0.0009022378495760277</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.002423061834759007</v>
+        <v>0.0006704446923609294</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.0005702862795874311</v>
+        <v>0.0005275987687280517</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.002710955427816221</v>
+        <v>0.00374878564289824</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.006044867235189297</v>
+        <v>0.004716340278273419</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.002059113642917601</v>
+        <v>0.008816405188908588</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.004857641334316888</v>
+        <v>0.009655897779507186</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.0001958228706063084</v>
+        <v>0.0003847424879130877</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.0002957408851385468</v>
+        <v>0.0003673620701746974</v>
       </c>
       <c r="CW4" t="n">
         <v>0</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.005059342520769831</v>
+        <v>0.009671009989509914</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.004603316393857275</v>
+        <v>0.00750767284945003</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.0004134239945140799</v>
+        <v>0.0003219519631187388</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.0003407923382224609</v>
+        <v>0.0004123154013945949</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.003650611443652758</v>
+        <v>0.001586181366170506</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.003083824300933175</v>
+        <v>0.006246572806675188</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.0006425330164760396</v>
+        <v>0.0006105054920596117</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.002795356599344724</v>
+        <v>0.00144945878144708</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.003365280620371695</v>
+        <v>0.00717241666457355</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.0008396745289095898</v>
+        <v>0.001211240591843336</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.002941237799444198</v>
+        <v>0.003070820611263221</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.00302029812070743</v>
+        <v>0.003536324579963549</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.002436498419832138</v>
+        <v>0.002518895954895267</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.001464495989531249</v>
+        <v>0.002633672480902009</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.0002087559186605938</v>
+        <v>0.000387960372488728</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.002202049145981721</v>
+        <v>0.001280723859623963</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.002331571058539472</v>
+        <v>0.003104275089507284</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.002802570752300305</v>
+        <v>0.002945803434200716</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.002549526149935001</v>
+        <v>0.002943440861548803</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.0003852523998972433</v>
+        <v>0.0003311391612990946</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.0004768275267374688</v>
+        <v>0.0002244228076646875</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.0002530510878274013</v>
+        <v>0.0004531681201027108</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.003397005390075769</v>
+        <v>0.001667485793469636</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.003723107645800366</v>
+        <v>0.002835365311607366</v>
       </c>
       <c r="DV4" t="n">
-        <v>2.196878993709557e-05</v>
+        <v>0</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.0008085006542647411</v>
+        <v>0.0003685283139816347</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.002195243811112737</v>
+        <v>0.001050937979828355</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.003332419797350028</v>
+        <v>0.001851834238343227</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.0005081540977579553</v>
+        <v>0.0003646760711086277</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.002987954110652163</v>
+        <v>0.002411505691150416</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.002470159616667412</v>
+        <v>0.004239172521201012</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.002125631763777816</v>
+        <v>0.001168494831151398</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.001389940149274096</v>
+        <v>0.001306905755327731</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.0001461717253131526</v>
+        <v>0.0001138530838219383</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.0008186741906218813</v>
+        <v>0.001292084265177289</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.0008224615463091648</v>
+        <v>0.00116645196424978</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.0003840416585341931</v>
+        <v>0.0004112181533532662</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.0008825838048904448</v>
+        <v>0.00126701696680464</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.001120156408957513</v>
+        <v>0.001528587485075565</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.0009344062493075592</v>
+        <v>0.0005017293579658103</v>
       </c>
       <c r="EL4" t="n">
-        <v>0.0001150904241095435</v>
+        <v>8.926440341333491e-05</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.0002390830149154379</v>
+        <v>0.0004655747157321373</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.0001281574248288909</v>
+        <v>0.0006528145399207128</v>
       </c>
       <c r="EO4" t="n">
         <v>0</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.0003196577796771287</v>
+        <v>0.0003201230045063795</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.001147592437101522</v>
+        <v>0.0007025369029193608</v>
       </c>
       <c r="ER4" t="n">
-        <v>4.884971893978924e-05</v>
+        <v>0.0001478565137323487</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.0001061281661069012</v>
+        <v>0.0002080089200297585</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.0009450823233084935</v>
+        <v>0.001082673766331111</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.001515554279803663</v>
+        <v>0.00073837928432727</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.0001698159142635321</v>
+        <v>0.0004779875677416473</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.001217814114903422</v>
+        <v>0.0009446980365373502</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.001612669298034385</v>
+        <v>0.001015125390137378</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.001951532656458324</v>
+        <v>0.001094401197039326</v>
       </c>
     </row>
     <row r="5">
@@ -2614,466 +2614,466 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.003881418092909561</v>
+        <v>-0.004278728606356974</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.004818560380725756</v>
+        <v>-0.003433984606275942</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.002587745389648999</v>
+        <v>-0.001747269890795622</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.00290112492599176</v>
+        <v>-0.0007976366322008821</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0009984399375975062</v>
+        <v>-0.002496099843993771</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.005797555625195838</v>
+        <v>-0.001272565847883966</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.007946210268948706</v>
+        <v>-0.003226761397276534</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.00278271166370635</v>
+        <v>-0.002806499261447548</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.005358200118413314</v>
+        <v>-0.002811735941320293</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.001817612033845139</v>
+        <v>-0.0008252284114353859</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0008252284114353192</v>
+        <v>-0.0009136457412319942</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.003718024985127888</v>
+        <v>-0.003033908387864437</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.005585023400936029</v>
+        <v>-0.008527801786228806</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.006020782396088065</v>
+        <v>-0.002505157677571523</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.001595273264401764</v>
+        <v>-0.0005327483547477474</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.00831122900088418</v>
+        <v>-0.002536125036862224</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.001528117359413228</v>
+        <v>-0.003227828267000943</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0028882994400236</v>
+        <v>-0.006387530562347166</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.001418020679468235</v>
+        <v>-0.001378878094641178</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.001243339253996478</v>
+        <v>-0.0008147916013789058</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.01870415647921764</v>
+        <v>-0.003514837222702449</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.001242971293282014</v>
+        <v>-0.004552002304811354</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.006876528117359471</v>
+        <v>-0.001591263650545993</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.0004128575641403454</v>
+        <v>-0.001509769094138591</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.005534181710565233</v>
+        <v>-0.005149452500739849</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.004118564742589726</v>
+        <v>-0.005145746579417076</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.0003545051698670587</v>
+        <v>-0.002604320804971838</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.006540396567031659</v>
+        <v>-0.002841918294849066</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.007749927974647075</v>
+        <v>-0.006576231200235894</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.003820293398533059</v>
+        <v>0.0005501222493887626</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.002292176039119831</v>
+        <v>-0.001536189069423921</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.001122599704579019</v>
+        <v>-0.001699798329011848</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.002304283604135882</v>
+        <v>-0.001716484166913257</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.00244886199942379</v>
+        <v>-0.001901469317199678</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.006643685365089291</v>
+        <v>-0.001880288310874334</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.002650532987611642</v>
+        <v>-0.003456425406203822</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.001310452418096719</v>
+        <v>-0.001872659176030001</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.007785314066646965</v>
+        <v>-0.003979943591350688</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.003807257584770951</v>
+        <v>-0.005447010065127334</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.005116002379535978</v>
+        <v>-0.000916870415647908</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.004897723998847581</v>
+        <v>-0.001844140392623483</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.003885929175806957</v>
+        <v>-0.004136634283923557</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.0004889975550121717</v>
+        <v>-0.002507051081165812</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0.002329696254792035</v>
+        <v>-0.002090483619344763</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0.0008271787296898036</v>
+        <v>-0.003082685105157068</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.0009672386895475893</v>
+        <v>-0.003039799435913526</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.001613367905502738</v>
+        <v>-0.00276577355229044</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.002231051344743318</v>
+        <v>-0.00399644760213147</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.001418020679468235</v>
+        <v>-0.0008552049542907336</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.004951425885302408</v>
+        <v>-0.001953240603728879</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.008221271393643082</v>
+        <v>-0.002486678507992945</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0.00177847113884555</v>
+        <v>-0.003906481207457802</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.003863167207313423</v>
+        <v>-0.007018578590386282</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0.0009748892171344114</v>
+        <v>-0.001684867394695788</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.003866745984532982</v>
+        <v>-0.001934477379095168</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.002919492774992572</v>
+        <v>-0.003037452079032677</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.008923556942277689</v>
+        <v>-0.00773790951638067</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.01176650366748169</v>
+        <v>-0.01897921760391196</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0.001857859038631615</v>
+        <v>-0.002367564368156216</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0.004570923031554053</v>
+        <v>-0.001650456822870661</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0.002901124925991738</v>
+        <v>-3.133813851459166e-05</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0.004055654233274153</v>
+        <v>-0.003670811130846696</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0.001487209994051164</v>
+        <v>-0.002012429712932784</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.003361094586555602</v>
+        <v>-0.001152405646787724</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0.00296411856474259</v>
+        <v>-0.002881014116969216</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0.006660772178013585</v>
+        <v>-0.007282415630550654</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.001302545885139172</v>
+        <v>-0.002241226776761973</v>
       </c>
       <c r="BQ5" t="n">
         <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0.001894865525672396</v>
+        <v>-0.00224648985959438</v>
       </c>
       <c r="BS5" t="n">
-        <v>-0.002093777646711836</v>
+        <v>-0.003226735811005521</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0.003777513384889952</v>
+        <v>-0.00316755476613384</v>
       </c>
       <c r="BU5" t="n">
-        <v>-0.001872659176029967</v>
+        <v>-0.002621722846441976</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.002592912705272266</v>
+        <v>-0.01042036708111315</v>
       </c>
       <c r="BW5" t="n">
-        <v>-8.643042350906516e-05</v>
+        <v>-2.94898260100207e-05</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.002017114914425466</v>
+        <v>-0.003111495246326745</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.006074904158065419</v>
+        <v>-0.008940201302545924</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.003493191237418625</v>
+        <v>-0.006897572528123197</v>
       </c>
       <c r="CA5" t="n">
-        <v>-0.0011281729865246</v>
+        <v>-0.001723597618301476</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0.002292176039119853</v>
+        <v>-0.002215288611544464</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0.00174607872151521</v>
+        <v>-0.003137951450562504</v>
       </c>
       <c r="CD5" t="n">
-        <v>-0.005624629958555416</v>
+        <v>-0.009147424511545332</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.002388675906812099</v>
+        <v>-0.003374777975133247</v>
       </c>
       <c r="CF5" t="n">
-        <v>-0.00225634597304919</v>
+        <v>-0.00263240363522409</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0.002152757298731889</v>
+        <v>-0.001642178046672471</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.002989934872705802</v>
+        <v>-0.006719952634695126</v>
       </c>
       <c r="CI5" t="n">
-        <v>-0.002241226776761973</v>
+        <v>-0.003789224393132062</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0.0001772525849335294</v>
+        <v>-0.0001784651992861708</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0.002486678507992945</v>
+        <v>-0.0008252284114353525</v>
       </c>
       <c r="CL5" t="n">
-        <v>-0.01219656601539376</v>
+        <v>-0.02323860272350508</v>
       </c>
       <c r="CM5" t="n">
-        <v>-0.001450133175495683</v>
+        <v>-0.0005014102162331669</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.0001181683899556862</v>
+        <v>-0.0006794682422451958</v>
       </c>
       <c r="CO5" t="n">
-        <v>-0.003995264871263682</v>
+        <v>-0.0007490636704120202</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.001538916839301541</v>
+        <v>-0.0008878366380585812</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.004853506954720333</v>
+        <v>-0.007694584196507814</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0.01589698046181177</v>
+        <v>-0.01311426879810543</v>
       </c>
       <c r="CS5" t="n">
-        <v>-0.005358200118413303</v>
+        <v>-0.02770870337477801</v>
       </c>
       <c r="CT5" t="n">
-        <v>-0.01518650088809953</v>
+        <v>-0.03022498519834227</v>
       </c>
       <c r="CU5" t="n">
-        <v>-0.0003133813851456946</v>
+        <v>-0.0006112469437652424</v>
       </c>
       <c r="CV5" t="n">
-        <v>-0.0002184087363494958</v>
+        <v>-0.0009714822939517643</v>
       </c>
       <c r="CW5" t="n">
         <v>0</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0.01494967436352876</v>
+        <v>-0.03025458851391361</v>
       </c>
       <c r="CY5" t="n">
-        <v>-0.006453522794553046</v>
+        <v>-0.02309058614564837</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-0.0003056234718826878</v>
+        <v>-0.0004439183190292906</v>
       </c>
       <c r="DA5" t="n">
-        <v>-0.0003256364712848292</v>
+        <v>-0.0005327019828351487</v>
       </c>
       <c r="DB5" t="n">
-        <v>-0.006954720331458997</v>
+        <v>-0.002989050014797246</v>
       </c>
       <c r="DC5" t="n">
-        <v>-0.01009473060982834</v>
+        <v>-0.0186796921255181</v>
       </c>
       <c r="DD5" t="n">
-        <v>-0.0004144464179988594</v>
+        <v>-0.0012433392539965</v>
       </c>
       <c r="DE5" t="n">
-        <v>-0.007339449541284382</v>
+        <v>-0.0004439183190292906</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.009325044404973403</v>
+        <v>-0.02309058614564837</v>
       </c>
       <c r="DG5" t="n">
-        <v>-0.001772616136919336</v>
+        <v>-0.002017114914425433</v>
       </c>
       <c r="DH5" t="n">
-        <v>-0.006781677572873279</v>
+        <v>-0.008496151568975785</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.008902333621434744</v>
+        <v>-0.01063094209161631</v>
       </c>
       <c r="DJ5" t="n">
-        <v>-0.007132331270262337</v>
+        <v>-0.007810197465369928</v>
       </c>
       <c r="DK5" t="n">
-        <v>-0.003006189213085786</v>
+        <v>-0.007191276156793447</v>
       </c>
       <c r="DL5" t="n">
-        <v>-0.0005328596802842478</v>
+        <v>-0.0009470257472624866</v>
       </c>
       <c r="DM5" t="n">
-        <v>-0.002475550122249415</v>
+        <v>-0.001268062518431112</v>
       </c>
       <c r="DN5" t="n">
-        <v>-0.006643685365089291</v>
+        <v>-0.006749555950266462</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.006662700773349195</v>
+        <v>-0.007726465364120838</v>
       </c>
       <c r="DP5" t="n">
-        <v>-0.007852468768590104</v>
+        <v>-0.009473060982830118</v>
       </c>
       <c r="DQ5" t="n">
-        <v>-0.0008880994671403908</v>
+        <v>-0.0006214856466410068</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.000275061124694409</v>
+        <v>-0.0006240249609984261</v>
       </c>
       <c r="DS5" t="n">
-        <v>-0.0005622965374371014</v>
+        <v>-0.001415511648481227</v>
       </c>
       <c r="DT5" t="n">
-        <v>-0.008447352766210569</v>
+        <v>-0.002249851983422191</v>
       </c>
       <c r="DU5" t="n">
-        <v>-0.009547888161808415</v>
+        <v>-0.005452836101535597</v>
       </c>
       <c r="DV5" t="n">
-        <v>-5.908419497784312e-05</v>
+        <v>0</v>
       </c>
       <c r="DW5" t="n">
-        <v>-0.001457465794170132</v>
+        <v>-0.0006338231057332666</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.004379141457793156</v>
+        <v>-0.002068317141961773</v>
       </c>
       <c r="DY5" t="n">
-        <v>-0.008466548253404416</v>
+        <v>-0.003212373587150541</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.0005014102162331335</v>
+        <v>-0.0008547008547008961</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.009136457412319488</v>
+        <v>-0.007161803713527903</v>
       </c>
       <c r="EB5" t="n">
-        <v>-0.005591909577632348</v>
+        <v>-0.01326228537596214</v>
       </c>
       <c r="EC5" t="n">
-        <v>-0.003582001184132655</v>
+        <v>-0.001435257410296409</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0.002945785020369773</v>
+        <v>-0.003399596658023662</v>
       </c>
       <c r="EE5" t="n">
         <v>-0.0001480165778567355</v>
       </c>
       <c r="EF5" t="n">
-        <v>-0.001368233194527047</v>
+        <v>-0.003108348134991157</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.002225007834534609</v>
+        <v>-0.002045520023048131</v>
       </c>
       <c r="EH5" t="n">
-        <v>-0.0008251833740831382</v>
+        <v>-0.001123244929797185</v>
       </c>
       <c r="EI5" t="n">
-        <v>-0.001880288310874312</v>
+        <v>-0.003374777975133236</v>
       </c>
       <c r="EJ5" t="n">
-        <v>-0.002036979003447159</v>
+        <v>-0.003071137574428074</v>
       </c>
       <c r="EK5" t="n">
-        <v>-0.001817612033845173</v>
+        <v>-0.0005622965374371014</v>
       </c>
       <c r="EL5" t="n">
-        <v>-0.0002379535990481685</v>
+        <v>-0.0002139364303178737</v>
       </c>
       <c r="EM5" t="n">
-        <v>-0.0004735128736312433</v>
+        <v>-0.0007834534628643475</v>
       </c>
       <c r="EN5" t="n">
-        <v>-0.0002444987775061413</v>
+        <v>-0.0005599764220454384</v>
       </c>
       <c r="EO5" t="n">
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.0003545051698670587</v>
+        <v>-0.0004420866489832531</v>
       </c>
       <c r="EQ5" t="n">
-        <v>-0.002475550122249404</v>
+        <v>-0.001650456822870661</v>
       </c>
       <c r="ER5" t="n">
-        <v>-2.947244326554355e-05</v>
+        <v>-0.0004420866489832642</v>
       </c>
       <c r="ES5" t="n">
-        <v>0</v>
+        <v>-0.0003569303985723193</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0.001786273895330592</v>
+        <v>-0.00179781903919839</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0.002964547677261642</v>
+        <v>-0.002045520023048153</v>
       </c>
       <c r="EV5" t="n">
-        <v>-0.0002881014116969283</v>
+        <v>-0.001535568787214037</v>
       </c>
       <c r="EW5" t="n">
-        <v>-0.002477672140593479</v>
+        <v>-0.002277691107644297</v>
       </c>
       <c r="EX5" t="n">
-        <v>-0.003791914760263226</v>
+        <v>-0.001444149720011845</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.005591909577632348</v>
+        <v>-0.002033598585322782</v>
       </c>
     </row>
     <row r="6">
@@ -3083,466 +3083,466 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.002472996249564418</v>
+        <v>-0.00204135543934359</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.0005209620642594198</v>
+        <v>-0.00076844453088471</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0008784984320734212</v>
+        <v>-0.0003043513965419381</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0009589168061374914</v>
+        <v>-0.0005453223751915343</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0004508706658922279</v>
+        <v>-0.0004175199324330719</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0008658651900257191</v>
+        <v>-6.851341036251125e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.001612137411733214</v>
+        <v>-0.001818792199020064</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.001798341472483644</v>
+        <v>-0.00143805761417698</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.001627740872014946</v>
+        <v>-0.001812103503342488</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0005452176817365762</v>
+        <v>-0.0003624808367608895</v>
       </c>
       <c r="L6" t="n">
-        <v>6.723490662457476e-05</v>
+        <v>-0.0001554174067495806</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.001334976545351787</v>
+        <v>-0.001641016189901293</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.001221524148372696</v>
+        <v>-0.00363528496580095</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.001767162201565384</v>
+        <v>-4.431314623338512e-05</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.0002722122943597722</v>
+        <v>-0.0001080380293863592</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.001970125122773633</v>
+        <v>5.253937694144051e-06</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.0002967085949730885</v>
+        <v>-0.000531757754800588</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.001612453196313771</v>
+        <v>-0.0009472622934360908</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0001968331048739697</v>
+        <v>-0.0004287806738045463</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0003257362039795486</v>
+        <v>-0.0003339359139760079</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.001850217149589692</v>
+        <v>-0.001330399432122545</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.000663495658147531</v>
+        <v>0.0001717095321230461</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.001566814396713814</v>
+        <v>8.158173932924228e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0.0003593816747633177</v>
+        <v>-0.0003356971384979201</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0006359727110995334</v>
+        <v>-0.001686021631985607</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.001012382934161771</v>
+        <v>-0.001139909325354912</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0001401772725159483</v>
+        <v>-0.001218363126946054</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.0005938366166959918</v>
+        <v>-0.001479072016184746</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.0007374553832048686</v>
+        <v>-0.002953834424480012</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.004367278322764489</v>
+        <v>0.003137214374482483</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.0009305301573392267</v>
+        <v>-0.0009806457771719401</v>
       </c>
       <c r="AG6" t="n">
-        <v>7.399952795894004e-05</v>
+        <v>-0.0005549241816947936</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.0001016056092677131</v>
+        <v>-0.0010117060099811</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.0005123988312119243</v>
+        <v>-0.0009582994770727133</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.00368848672039796</v>
+        <v>0.001078689824106993</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.002171828084349364</v>
+        <v>0.002999403122192287</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.001014575385183739</v>
+        <v>-0.0004475333792872211</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0.0006724309889898417</v>
+        <v>0.002992632398474748</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.001823736966987249</v>
+        <v>-0.001886207360202371</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.002449121759119116</v>
+        <v>0.0007184049211609866</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.003022530314415531</v>
+        <v>-0.001482831684905531</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.001322546548037809</v>
+        <v>-0.0001034983924072835</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.002901915237874181</v>
+        <v>0.00388127137558554</v>
       </c>
       <c r="AS6" t="n">
-        <v>-0.001142600288363641</v>
+        <v>-0.001306519023393812</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0.0001620521811034892</v>
+        <v>-0.0006254434893788518</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.0003941731429838335</v>
+        <v>-0.0008847731875191057</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.001072691662884295</v>
+        <v>-0.001086507612112547</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.0009350009395463071</v>
+        <v>-0.001424883489051504</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.0009036066096735129</v>
+        <v>-0.0001338488994646364</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.0003018661672458928</v>
+        <v>-0.001366452817359887</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.0001042455838932477</v>
+        <v>-0.0003989077656015804</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.0004795625051454865</v>
+        <v>-0.001989880573218045</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0.0008986042412581718</v>
+        <v>-0.0004812227939634512</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0.0007182027828044252</v>
+        <v>-0.0002506376626480899</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.0007684465386859047</v>
+        <v>-0.0006116478679398602</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.002431968978025636</v>
+        <v>-0.002174165957497232</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.003403798916847808</v>
+        <v>-0.002444832742729658</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.001333853354134162</v>
+        <v>-0.00181259612794773</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0.0007449987888485998</v>
+        <v>-0.0005907205368792051</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0.002809781356771526</v>
+        <v>-0.0005998751028327753</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-0.0001973146052509395</v>
+        <v>0.0003721734545617417</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0.00154294558090394</v>
+        <v>-0.002738905705301217</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0.0004856787664288042</v>
+        <v>-0.000951709200083578</v>
       </c>
       <c r="BM6" t="n">
-        <v>-0.001046793218261277</v>
+        <v>-0.0004879773053128866</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0.001848618682850262</v>
+        <v>-0.0008274377881217848</v>
       </c>
       <c r="BO6" t="n">
-        <v>-0.001345928143842545</v>
+        <v>-0.0009952454332892158</v>
       </c>
       <c r="BP6" t="n">
-        <v>-0.0004742217806071869</v>
+        <v>-0.00127291409641731</v>
       </c>
       <c r="BQ6" t="n">
         <v>0</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0.001085215234593409</v>
+        <v>-0.0009089205349123082</v>
       </c>
       <c r="BS6" t="n">
-        <v>-0.000290597360713371</v>
+        <v>-0.001039743894947276</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0.0005474039679265602</v>
+        <v>8.600876783425304e-05</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0.001726319664033535</v>
+        <v>-0.001189371052329022</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0.001016729666741689</v>
+        <v>-0.002362391086081764</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0.000842028464103811</v>
+        <v>-0.0007324725309861474</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.00163912654236458</v>
+        <v>-0.003143627702770874</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.001257688265965884</v>
+        <v>-0.001855839757220448</v>
       </c>
       <c r="CA6" t="n">
-        <v>-0.0002973784053424411</v>
+        <v>-0.0006975713794388661</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0.0006550127561318952</v>
+        <v>-0.001322495102628235</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0.0005370646442199062</v>
+        <v>-0.001117242576375982</v>
       </c>
       <c r="CD6" t="n">
-        <v>-0.002132584564830148</v>
+        <v>-0.0008506323006011451</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.002036801501197697</v>
+        <v>-0.000811258679746582</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0.001253178543470268</v>
+        <v>-0.0009469687797813237</v>
       </c>
       <c r="CG6" t="n">
-        <v>-0.0005436599486451421</v>
+        <v>-0.001127854647530513</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.001683394162983493</v>
+        <v>-0.001050045911356709</v>
       </c>
       <c r="CI6" t="n">
-        <v>-0.001285606323156799</v>
+        <v>-0.001392356091029562</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-2.292176039120075e-05</v>
+        <v>-3.028987120758941e-05</v>
       </c>
       <c r="CK6" t="n">
-        <v>-0.001567673691515239</v>
+        <v>-0.0004586244122332328</v>
       </c>
       <c r="CL6" t="n">
-        <v>-0.001915861451431059</v>
+        <v>-0.001715110628692648</v>
       </c>
       <c r="CM6" t="n">
-        <v>-0.0006909463400574661</v>
+        <v>3.900156006240163e-05</v>
       </c>
       <c r="CN6" t="n">
-        <v>-7.411780104604748e-06</v>
+        <v>-0.0002422385741517402</v>
       </c>
       <c r="CO6" t="n">
-        <v>-0.0002006795201857786</v>
+        <v>-0.0002366439485165822</v>
       </c>
       <c r="CP6" t="n">
-        <v>-0.0002876434144252537</v>
+        <v>-8.880994671405795e-05</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.0003644525413565886</v>
+        <v>-0.0003041998197478496</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.00150687842052078</v>
+        <v>-0.0009166980925170403</v>
       </c>
       <c r="CS6" t="n">
-        <v>-0.0001799205679084981</v>
+        <v>-0.002845488532184998</v>
       </c>
       <c r="CT6" t="n">
-        <v>-0.001570256770489345</v>
+        <v>-0.002987023080174322</v>
       </c>
       <c r="CU6" t="n">
-        <v>-0.0001548219106464105</v>
+        <v>-0.0001953297225186224</v>
       </c>
       <c r="CV6" t="n">
-        <v>4.439183190292906e-05</v>
+        <v>-9.580285416888601e-05</v>
       </c>
       <c r="CW6" t="n">
         <v>0</v>
       </c>
       <c r="CX6" t="n">
-        <v>-0.002623737176484042</v>
+        <v>-0.001680568266154584</v>
       </c>
       <c r="CY6" t="n">
-        <v>-0.0006216573277213506</v>
+        <v>-0.001665928269912184</v>
       </c>
       <c r="CZ6" t="n">
-        <v>-0.0001990563255676647</v>
+        <v>0</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.0001031796255461431</v>
+        <v>-3.528072014291894e-05</v>
       </c>
       <c r="DB6" t="n">
-        <v>-5.374236161804211e-05</v>
+        <v>0.0004729399081955882</v>
       </c>
       <c r="DC6" t="n">
-        <v>-0.002358051856724819</v>
+        <v>-0.000280510617698021</v>
       </c>
       <c r="DD6" t="n">
-        <v>-0.0002619195795550977</v>
+        <v>-0.000604870375882538</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.0004867433173518898</v>
+        <v>0.0006490636653545434</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.0008630880528252949</v>
+        <v>-0.002481750582320538</v>
       </c>
       <c r="DG6" t="n">
-        <v>-0.0006050129645635393</v>
+        <v>-0.000363191820506778</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0.001131243067475551</v>
+        <v>-0.001213052408025511</v>
       </c>
       <c r="DI6" t="n">
-        <v>-0.00196511057600387</v>
+        <v>-0.00250164873380018</v>
       </c>
       <c r="DJ6" t="n">
-        <v>-0.0006967399387517226</v>
+        <v>-0.001976487407436495</v>
       </c>
       <c r="DK6" t="n">
-        <v>-0.0007358986932338413</v>
+        <v>-0.001087856139976489</v>
       </c>
       <c r="DL6" t="n">
-        <v>-5.141120019073741e-05</v>
+        <v>-0.0001335086079287701</v>
       </c>
       <c r="DM6" t="n">
-        <v>-0.0003905838075091012</v>
+        <v>-0.0006199865972167429</v>
       </c>
       <c r="DN6" t="n">
-        <v>-0.001404779464984773</v>
+        <v>-0.002018250224503023</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.003032343805348273</v>
+        <v>-0.001952919037545556</v>
       </c>
       <c r="DP6" t="n">
-        <v>-0.003475609085380651</v>
+        <v>-0.001995465191653964</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0.0002542509004507171</v>
+        <v>-0.0002072753404558925</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.834534628642365e-06</v>
+        <v>-0.0002154583925386255</v>
       </c>
       <c r="DS6" t="n">
-        <v>-0.0002913765031875099</v>
+        <v>-3.028987120758941e-05</v>
       </c>
       <c r="DT6" t="n">
-        <v>-0.003023266138548775</v>
+        <v>-0.0009372011512661371</v>
       </c>
       <c r="DU6" t="n">
-        <v>-0.002277276436780504</v>
+        <v>-0.002554559364141257</v>
       </c>
       <c r="DV6" t="n">
         <v>0</v>
       </c>
       <c r="DW6" t="n">
-        <v>-0.0001404056162246814</v>
+        <v>-0.0003564382362150925</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.002028258995246218</v>
+        <v>-0.0005477068235419352</v>
       </c>
       <c r="DY6" t="n">
-        <v>-0.003676816602988265</v>
+        <v>-0.0008279929751551286</v>
       </c>
       <c r="DZ6" t="n">
-        <v>-7.25844439769531e-07</v>
+        <v>1.477104874445245e-05</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.0004513517366142028</v>
+        <v>-0.001258090536208167</v>
       </c>
       <c r="EB6" t="n">
-        <v>-0.003253071434465246</v>
+        <v>-0.002271469790117653</v>
       </c>
       <c r="EC6" t="n">
-        <v>-0.0007825388867133215</v>
+        <v>-0.000829065757815528</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0.0003389244061815427</v>
+        <v>-0.001659280370799163</v>
       </c>
       <c r="EE6" t="n">
-        <v>-2.160760587726629e-05</v>
+        <v>-2.967626072717389e-05</v>
       </c>
       <c r="EF6" t="n">
-        <v>-0.0005832592854276064</v>
+        <v>-0.001166959140529564</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.000713468038829429</v>
+        <v>-0.0009023679732208217</v>
       </c>
       <c r="EH6" t="n">
-        <v>7.368110816369234e-06</v>
+        <v>-0.000395823054020325</v>
       </c>
       <c r="EI6" t="n">
-        <v>-0.001210564281923732</v>
+        <v>-0.001115646119546346</v>
       </c>
       <c r="EJ6" t="n">
-        <v>-0.001480096657741006</v>
+        <v>-0.0007530622826298572</v>
       </c>
       <c r="EK6" t="n">
-        <v>-0.0008228823534963904</v>
+        <v>-0.0003560179707365829</v>
       </c>
       <c r="EL6" t="n">
-        <v>-2.95683724539697e-05</v>
+        <v>0</v>
       </c>
       <c r="EM6" t="n">
-        <v>7.640586797064142e-06</v>
+        <v>-0.0003994450662933802</v>
       </c>
       <c r="EN6" t="n">
-        <v>0</v>
+        <v>-8.620510549927073e-05</v>
       </c>
       <c r="EO6" t="n">
         <v>0</v>
       </c>
       <c r="EP6" t="n">
-        <v>6.632603440584195e-05</v>
+        <v>-0.0001322629324346542</v>
       </c>
       <c r="EQ6" t="n">
-        <v>-0.0009938402273380583</v>
+        <v>-0.001079291888056932</v>
       </c>
       <c r="ER6" t="n">
         <v>0</v>
       </c>
       <c r="ES6" t="n">
-        <v>0</v>
+        <v>-0.0002648111253046676</v>
       </c>
       <c r="ET6" t="n">
-        <v>-0.0005723997423225962</v>
+        <v>-0.001318912942732536</v>
       </c>
       <c r="EU6" t="n">
-        <v>-0.000462609515616591</v>
+        <v>-0.001072197115221416</v>
       </c>
       <c r="EV6" t="n">
-        <v>-0.0001549067037236201</v>
+        <v>-0.0002009868021133537</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0.0008862308515329182</v>
+        <v>-0.0008282915586286965</v>
       </c>
       <c r="EX6" t="n">
-        <v>-0.001099015253892177</v>
+        <v>-0.0007451718359385906</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.0003329723786911071</v>
+        <v>-0.0008807769322964259</v>
       </c>
     </row>
     <row r="7">
@@ -3552,466 +3552,466 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.0001697864074090339</v>
+        <v>7.581734894152592e-05</v>
       </c>
       <c r="C7" t="n">
-        <v>3.700827501341709e-05</v>
+        <v>5.969050215413053e-05</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0002448277706389168</v>
+        <v>0.0001621679689384425</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0002512691349603802</v>
+        <v>0.000753339774053724</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0004579331761821904</v>
+        <v>-7.529455841392419e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>8.855663824338666e-05</v>
+        <v>0.0005601088685246169</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0002536696757731382</v>
+        <v>-0.001209528028607598</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.001225817622662678</v>
+        <v>7.399044212391117e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0001076907718007502</v>
+        <v>-0.0007592610450314007</v>
       </c>
       <c r="K7" t="n">
-        <v>-8.558997922082369e-05</v>
+        <v>3.586660320326063e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0002624289242562639</v>
+        <v>0.0001026653848919756</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0005601727305041104</v>
+        <v>-0.0007379100836663488</v>
       </c>
       <c r="N7" t="n">
-        <v>0.001830306691572314</v>
+        <v>0.002480691799098594</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0009740512979080796</v>
+        <v>0.0004402905186544736</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0004065240087331445</v>
+        <v>0.0002662461858948084</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.003355808291983309</v>
+        <v>0.003398474320405365</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0006235734087794098</v>
+        <v>0.0004079780910466235</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0002416352619307782</v>
+        <v>-0.000250872607000785</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0001800341676588324</v>
+        <v>-0.0002663390158518797</v>
       </c>
       <c r="U7" t="n">
-        <v>0.000605273233910103</v>
+        <v>0.0007717354484430339</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.001008121223725345</v>
+        <v>0.0001135677611012353</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.0001428025149425416</v>
+        <v>0.0007243321881654162</v>
       </c>
       <c r="X7" t="n">
-        <v>0.001331230385957577</v>
+        <v>0.00114045503017845</v>
       </c>
       <c r="Y7" t="n">
-        <v>-4.632303659088954e-05</v>
+        <v>-0.0001077473200058521</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.002848973924983067</v>
+        <v>0.001547900038234074</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.001971861382956547</v>
+        <v>0.001272130648889175</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0003988503332839288</v>
+        <v>-0.0003056791798884184</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.0003434115542150618</v>
+        <v>-0.0001198474905288627</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.002122218874085019</v>
+        <v>0.002244176090311806</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.006413986896554503</v>
+        <v>0.006467944406810366</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.0003202230633458814</v>
+        <v>0.00069182874394092</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.0003553588271384245</v>
+        <v>0.0004221066366941695</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.0008620575727059543</v>
+        <v>-0.0002655391127874662</v>
       </c>
       <c r="AI7" t="n">
-        <v>8.900813172447731e-05</v>
+        <v>-0.0005915540557697885</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.001180690741457885</v>
+        <v>0.00471231972172918</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.01491932549178984</v>
+        <v>0.01243296646396006</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.0005158807449862135</v>
+        <v>-2.454441921734274e-06</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.004011023073214964</v>
+        <v>0.004378180087437311</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.0001163950643283507</v>
+        <v>-0.000948125975063302</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.0001801043713614559</v>
+        <v>0.001209919210073435</v>
       </c>
       <c r="AP7" t="n">
-        <v>-0.001842610026036734</v>
+        <v>-0.0005170145125027725</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.0007359942878989113</v>
+        <v>0.0003120709098026642</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.004533724645340759</v>
+        <v>0.006349109793877572</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.001167830850290447</v>
+        <v>-0.0006283828483166943</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.0009211496725575807</v>
+        <v>0.0002499294348302206</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.434875761230255e-05</v>
+        <v>-4.282300503842263e-05</v>
       </c>
       <c r="AV7" t="n">
-        <v>-0.0007271367591767663</v>
+        <v>-0.0003804205580859143</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.0002222085210323243</v>
+        <v>-0.0008785924470686879</v>
       </c>
       <c r="AX7" t="n">
-        <v>-0.0004599063589435626</v>
+        <v>0.0003695909612897064</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.001331417920818623</v>
+        <v>-0.0002253653364525599</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.0002409659604774794</v>
+        <v>0.001195090445297953</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.00138084840582709</v>
+        <v>0.001889099959184709</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.0006462815969851099</v>
+        <v>0.001406682008194732</v>
       </c>
       <c r="BC7" t="n">
-        <v>-0.0004872111489045705</v>
+        <v>-7.421961539291755e-05</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.0004534447752087501</v>
+        <v>-0.0001330446857290946</v>
       </c>
       <c r="BE7" t="n">
-        <v>-0.0006510280702399062</v>
+        <v>0.0001798032091819002</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.0008279697617578019</v>
+        <v>0.0007772993539020668</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.0001183782184078441</v>
+        <v>-0.000134613464750899</v>
       </c>
       <c r="BH7" t="n">
-        <v>-0.000234009360374432</v>
+        <v>-0.0002444189645268102</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.003068475826646594</v>
+        <v>0.003902439227253829</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.0007308668958711295</v>
+        <v>0.001504253635210595</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0.0007536138564305017</v>
+        <v>-0.001514400913414454</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.0002301759552044202</v>
+        <v>-0.000485699559944508</v>
       </c>
       <c r="BM7" t="n">
-        <v>-0.0002472188775191619</v>
+        <v>0.0006604953853326268</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.0001641359285999566</v>
+        <v>0.001594149427605557</v>
       </c>
       <c r="BO7" t="n">
-        <v>-0.00043601850645964</v>
+        <v>0.0003368062958456597</v>
       </c>
       <c r="BP7" t="n">
-        <v>1.341161744106145e-05</v>
+        <v>-0.0002418571174095219</v>
       </c>
       <c r="BQ7" t="n">
         <v>0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-5.052559802431968e-07</v>
+        <v>0.0003839688601376567</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.0003208853654417309</v>
+        <v>-0.0002158416032895849</v>
       </c>
       <c r="BT7" t="n">
-        <v>-0.0002507775123687716</v>
+        <v>0.0005361046012401727</v>
       </c>
       <c r="BU7" t="n">
-        <v>-5.920608987019854e-07</v>
+        <v>0.0007032182170420009</v>
       </c>
       <c r="BV7" t="n">
-        <v>-0.0007973773167818887</v>
+        <v>-0.0003085778639054626</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>1.341161744103924e-05</v>
+        <v>0.0001383275617770852</v>
       </c>
       <c r="BY7" t="n">
-        <v>-0.0003857592085680873</v>
+        <v>-0.0001131329587379992</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0.000187626110548167</v>
+        <v>-4.6162971213215e-05</v>
       </c>
       <c r="CA7" t="n">
-        <v>8.862629246676468e-05</v>
+        <v>2.966875172420446e-05</v>
       </c>
       <c r="CB7" t="n">
-        <v>-4.384270292331351e-05</v>
+        <v>-0.0005617981948633055</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.0006198616405920399</v>
+        <v>0.000617227052449898</v>
       </c>
       <c r="CD7" t="n">
-        <v>-4.339339505187722e-05</v>
+        <v>-0.000170615982689537</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.0009000588142848653</v>
+        <v>-0.0003899831475195459</v>
       </c>
       <c r="CF7" t="n">
-        <v>-0.0005172227630647675</v>
+        <v>-0.0002747416742635456</v>
       </c>
       <c r="CG7" t="n">
-        <v>-0.0003296463955346329</v>
+        <v>-0.0004128575641403565</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.0003401013209138159</v>
+        <v>-0.0004274634151895496</v>
       </c>
       <c r="CI7" t="n">
-        <v>-0.0004853304755819244</v>
+        <v>-0.0003640234064523961</v>
       </c>
       <c r="CJ7" t="n">
+        <v>-5.551115123125783e-18</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0.000253148328054531</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>0.0002009390318685966</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>0.0002645478885829278</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>0.0003133969972291484</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>0.0001114183077442044</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>1.477104874446078e-05</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>0.0003221824472001034</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>8.023927314061431e-05</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>-0.000562341685158485</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>3.457609568713327e-06</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>-6.000559738199018e-05</v>
+      </c>
+      <c r="CV7" t="n">
         <v>0</v>
-      </c>
-      <c r="CK7" t="n">
-        <v>-0.0002788553693640394</v>
-      </c>
-      <c r="CL7" t="n">
-        <v>0.0001265164142395914</v>
-      </c>
-      <c r="CM7" t="n">
-        <v>1.734822943205708e-06</v>
-      </c>
-      <c r="CN7" t="n">
-        <v>0.0007776345546901153</v>
-      </c>
-      <c r="CO7" t="n">
-        <v>0.0005689793163656919</v>
-      </c>
-      <c r="CP7" t="n">
-        <v>0.0001095465943363461</v>
-      </c>
-      <c r="CQ7" t="n">
-        <v>0.000498422333000198</v>
-      </c>
-      <c r="CR7" t="n">
-        <v>7.379409600301589e-05</v>
-      </c>
-      <c r="CS7" t="n">
-        <v>0.0005230433428340287</v>
-      </c>
-      <c r="CT7" t="n">
-        <v>-0.0002126017093859622</v>
-      </c>
-      <c r="CU7" t="n">
-        <v>-2.927717052535473e-05</v>
-      </c>
-      <c r="CV7" t="n">
-        <v>0.0002188521691784517</v>
       </c>
       <c r="CW7" t="n">
         <v>0</v>
       </c>
       <c r="CX7" t="n">
-        <v>8.60365873646407e-05</v>
+        <v>-0.0006552675900139693</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.0007305628320419422</v>
+        <v>-0.0005940557271303716</v>
       </c>
       <c r="CZ7" t="n">
+        <v>8.871811959037523e-05</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>0.0001768781164544875</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>0.001076572056812225</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>-1.458782011710125e-05</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>-1.579129844380689e-05</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>0.0007576991063650174</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>-0.001347619189540972</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>-0.0001814988977158705</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>-0.0003396042777789543</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>-0.0008130016455536904</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>-0.000830383496488124</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>-0.0002210952878568317</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>0.0001483687886308871</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>0.0006784705644418742</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>-0.0002814630113967376</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>-3.133813851458056e-05</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>-0.0009805231623767952</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>-3.044011800174551e-05</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>-8.843471254113555e-05</v>
+      </c>
+      <c r="DS7" t="n">
         <v>0</v>
       </c>
-      <c r="DA7" t="n">
-        <v>0.000358872781877545</v>
-      </c>
-      <c r="DB7" t="n">
-        <v>0.001421105974289133</v>
-      </c>
-      <c r="DC7" t="n">
-        <v>-0.001043181568625751</v>
-      </c>
-      <c r="DD7" t="n">
-        <v>-0.0001059868597918845</v>
-      </c>
-      <c r="DE7" t="n">
-        <v>0.0007254910886090483</v>
-      </c>
-      <c r="DF7" t="n">
-        <v>0.0002323974770340797</v>
-      </c>
-      <c r="DG7" t="n">
-        <v>0.0002002409792646543</v>
-      </c>
-      <c r="DH7" t="n">
-        <v>-0.0005714905670070713</v>
-      </c>
-      <c r="DI7" t="n">
-        <v>-0.0002852410497918123</v>
-      </c>
-      <c r="DJ7" t="n">
-        <v>-0.0006228472939983464</v>
-      </c>
-      <c r="DK7" t="n">
-        <v>-0.000133227860004731</v>
-      </c>
-      <c r="DL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM7" t="n">
-        <v>-8.823416279204465e-05</v>
-      </c>
-      <c r="DN7" t="n">
-        <v>-0.00011083938550418</v>
-      </c>
-      <c r="DO7" t="n">
-        <v>-0.0009723611647820762</v>
-      </c>
-      <c r="DP7" t="n">
-        <v>-0.0017923094889915</v>
-      </c>
-      <c r="DQ7" t="n">
-        <v>8.6440239218111e-07</v>
-      </c>
-      <c r="DR7" t="n">
-        <v>0.000116430326281225</v>
-      </c>
-      <c r="DS7" t="n">
-        <v>-3.056234718826767e-05</v>
-      </c>
       <c r="DT7" t="n">
-        <v>-0.0001670051964643149</v>
+        <v>-8.739695685182068e-05</v>
       </c>
       <c r="DU7" t="n">
-        <v>-0.0009305499351615677</v>
+        <v>-0.001495246018713414</v>
       </c>
       <c r="DV7" t="n">
         <v>0</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.0002063766338367634</v>
+        <v>5.923402589104176e-05</v>
       </c>
       <c r="DX7" t="n">
-        <v>-0.001439956048004104</v>
+        <v>-0.0001478154016706701</v>
       </c>
       <c r="DY7" t="n">
-        <v>-0.001772583782655324</v>
+        <v>-0.0002353879771453904</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.0002444235700462149</v>
+        <v>0.0002068476964379118</v>
       </c>
       <c r="EA7" t="n">
-        <v>8.049184596628511e-05</v>
+        <v>-0.0001951508446865979</v>
       </c>
       <c r="EB7" t="n">
-        <v>-0.0008401906087463107</v>
+        <v>-0.001314552826611842</v>
       </c>
       <c r="EC7" t="n">
-        <v>-0.0004067113483661733</v>
+        <v>-0.000280702383257786</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.0004745687971543844</v>
+        <v>-0.0004745603905847662</v>
       </c>
       <c r="EE7" t="n">
-        <v>1.528117359412828e-05</v>
+        <v>-1.440507058484974e-05</v>
       </c>
       <c r="EF7" t="n">
-        <v>-0.0002066734368680489</v>
+        <v>0.0001384889136396839</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.0002554248844618578</v>
+        <v>-0.0002094366201280395</v>
       </c>
       <c r="EH7" t="n">
-        <v>0.0001018550213544411</v>
+        <v>-0.0001953855449556008</v>
       </c>
       <c r="EI7" t="n">
-        <v>-0.0007240716661245262</v>
+        <v>-0.0009065473242558686</v>
       </c>
       <c r="EJ7" t="n">
-        <v>-0.0003411980337610532</v>
+        <v>0.0001478680444178648</v>
       </c>
       <c r="EK7" t="n">
-        <v>-5.903201631600185e-05</v>
+        <v>-9.042233349241814e-05</v>
       </c>
       <c r="EL7" t="n">
         <v>0</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.0001210154967002053</v>
+        <v>-0.000109204368174709</v>
       </c>
       <c r="EN7" t="n">
-        <v>1.479727730097635e-05</v>
+        <v>6.028536907880522e-05</v>
       </c>
       <c r="EO7" t="n">
         <v>0</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.0001203138035804186</v>
+        <v>4.597229679437765e-05</v>
       </c>
       <c r="EQ7" t="n">
-        <v>-0.0003940355931005446</v>
+        <v>-0.000570269699100101</v>
       </c>
       <c r="ER7" t="n">
         <v>0</v>
       </c>
       <c r="ES7" t="n">
-        <v>2.953787941843422e-05</v>
+        <v>-1.479727730097635e-05</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.0001042434553520988</v>
+        <v>4.525223449903249e-05</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.000177466848221991</v>
+        <v>-0.0006044985309489215</v>
       </c>
       <c r="EV7" t="n">
-        <v>-3.133813851456946e-05</v>
+        <v>-8.778979318974089e-05</v>
       </c>
       <c r="EW7" t="n">
-        <v>-0.0001633686314270133</v>
+        <v>-0.0004392828638845825</v>
       </c>
       <c r="EX7" t="n">
-        <v>-7.239133108383756e-05</v>
+        <v>-0.0003538779121203151</v>
       </c>
       <c r="EY7" t="n">
-        <v>4.176252198501151e-05</v>
+        <v>-0.0007031998624288549</v>
       </c>
     </row>
     <row r="8">
@@ -4021,466 +4021,466 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002018247069364693</v>
+        <v>0.0009920603720700138</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0006859526405089356</v>
+        <v>0.0004511684615783357</v>
       </c>
       <c r="D8" t="n">
-        <v>7.921713824274868e-05</v>
+        <v>0.0005252905016646575</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0008386540906021533</v>
+        <v>0.001590681098811683</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0009585742038121264</v>
+        <v>0.0006707244605171275</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0007730501732304439</v>
+        <v>0.001064236680276928</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001599568918074601</v>
+        <v>0.0008256064861277862</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001574784036019911</v>
+        <v>0.002251409606805202</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001873873615821977</v>
+        <v>0.0004377948203891868</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0004847788403234438</v>
+        <v>0.000204857296095412</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0003212941847075629</v>
+        <v>0.0003168986961738757</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0004825406499406077</v>
+        <v>0.0007216959283984275</v>
       </c>
       <c r="N8" t="n">
-        <v>0.003634324469398065</v>
+        <v>0.003002336023228511</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0008782769476512215</v>
+        <v>0.001064889851549183</v>
       </c>
       <c r="P8" t="n">
-        <v>0.001085844286154244</v>
+        <v>0.0006023032428227437</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.009444158846035217</v>
+        <v>0.007063037913483422</v>
       </c>
       <c r="R8" t="n">
-        <v>0.0007621145370589666</v>
+        <v>0.001192459421289807</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0005169211346648412</v>
+        <v>0.0006318252730109191</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0003697293483481718</v>
+        <v>0.0003922623670087055</v>
       </c>
       <c r="U8" t="n">
-        <v>0.001236166262263347</v>
+        <v>0.001496334672057617</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0001771738992639826</v>
+        <v>0.0009625136304203279</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0002511910962438829</v>
+        <v>0.001864992482397612</v>
       </c>
       <c r="X8" t="n">
-        <v>0.003416033613163652</v>
+        <v>0.003627760685854583</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0002472179402913388</v>
+        <v>0.0001848612376702863</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.004781121654970269</v>
+        <v>0.003475783148105665</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.00371431744658117</v>
+        <v>0.003938552752167129</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0007276795926079466</v>
+        <v>0.0003855335897335305</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.002759437860585415</v>
+        <v>0.001499216002186599</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.005265123793964557</v>
+        <v>0.005295624121953268</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.007670222984894726</v>
+        <v>0.01205994740677723</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.001330297510849879</v>
+        <v>0.001555362346350694</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0006308559715845375</v>
+        <v>0.001134356696226646</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.001454136775630563</v>
+        <v>-1.391879369073146e-05</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.0004617969061450538</v>
+        <v>0.00104783377312393</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.003686399566466186</v>
+        <v>0.008360653294787319</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.02497254009129068</v>
+        <v>0.0251929094748854</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.001286851668332889</v>
+        <v>0.0006339013199910259</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.00506092738530495</v>
+        <v>0.006510085122505993</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.001169542713517913</v>
+        <v>-0.0002872815491904796</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.001288480195042358</v>
+        <v>0.002697378161894692</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.967997405348144e-05</v>
+        <v>-0.0001448150656365082</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.0005275236193484772</v>
+        <v>0.001779049010793024</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.00552430309915499</v>
+        <v>0.01162493799929614</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.001640616283368399</v>
+        <v>0.0002278335035668544</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.001914688221542618</v>
+        <v>0.0009601999624228835</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.001065726859992641</v>
+        <v>0.0008028820703230605</v>
       </c>
       <c r="AV8" t="n">
-        <v>-0.0003634871153323061</v>
+        <v>0.00020756355557566</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.002458003521615085</v>
+        <v>-0.0007160760659647297</v>
       </c>
       <c r="AX8" t="n">
-        <v>-7.80031201250142e-06</v>
+        <v>0.0009345338122557695</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.002950206978769937</v>
+        <v>0.00071843955511878</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.0008395449283085499</v>
+        <v>0.001835507002073711</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.004328255943965534</v>
+        <v>0.00300199910418606</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.001821911623083355</v>
+        <v>0.003852125799052667</v>
       </c>
       <c r="BC8" t="n">
-        <v>-3.820293398535679e-05</v>
+        <v>0.0003043831635276079</v>
       </c>
       <c r="BD8" t="n">
-        <v>-0.0002211345839001067</v>
+        <v>0.0002732775160507822</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.0009216856935711838</v>
+        <v>0.001918938826518571</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.002229197880587919</v>
+        <v>0.006563082545351129</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.001553461451180238</v>
+        <v>0.00118609035525144</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.134368166826111e-05</v>
+        <v>0.000464190981432322</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.01048408697563252</v>
+        <v>0.01118268226992914</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.002042758502467396</v>
+        <v>0.002618305845546889</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.002936043202030061</v>
+        <v>0.0001663407035168846</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.000499653810194367</v>
+        <v>-2.720641685348413e-05</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.001022628890073923</v>
+        <v>0.001433216171884205</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.001577420016272951</v>
+        <v>0.004660668364079865</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.000795440763243191</v>
+        <v>0.0009516752603749624</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.001124173417969962</v>
+        <v>0.0007540886732420149</v>
       </c>
       <c r="BQ8" t="n">
         <v>0</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.0007067362969801787</v>
+        <v>0.002548253919870952</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.000718704451048699</v>
+        <v>0.001013791122153662</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.0002953294998011613</v>
+        <v>0.000957416089008503</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.001138735798475665</v>
+        <v>0.001107489647709386</v>
       </c>
       <c r="BV8" t="n">
-        <v>-0.0003833681386780863</v>
+        <v>0.001191207004876638</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>8.188863362963983e-05</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.0008849501318137943</v>
+        <v>0.0009901309577131008</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.002369245520832955</v>
+        <v>0.001211721437838303</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.002265518148982118</v>
+        <v>0.000420139038536596</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.0004752065106572806</v>
+        <v>0.0005578644230061963</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.0006644415018181942</v>
+        <v>0.0003376749673894758</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.002093385590650912</v>
+        <v>0.001337000935593144</v>
       </c>
       <c r="CD8" t="n">
-        <v>0.0008880332947621388</v>
+        <v>0.000869901707028567</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.000191917115956397</v>
+        <v>0.0009874999846588629</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.0008476477602620796</v>
+        <v>0.0007727132044705237</v>
       </c>
       <c r="CG8" t="n">
-        <v>-0.0001921285479040524</v>
+        <v>0.0003629349672359117</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.0006959322993946388</v>
+        <v>0.0006275169436494449</v>
       </c>
       <c r="CI8" t="n">
-        <v>7.028415047055651e-06</v>
+        <v>-5.185024739972066e-05</v>
       </c>
       <c r="CJ8" t="n">
-        <v>2.23081499107658e-05</v>
+        <v>6.660746003550599e-05</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.0002315206345329085</v>
+        <v>0.000833869282560587</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.001080117139111458</v>
+        <v>0.0005863609211882725</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.001480481277641007</v>
+        <v>0.0008395254202435226</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.002273182724063749</v>
+        <v>0.0008359506794064691</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.002174667593485419</v>
+        <v>0.0006931415899329135</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.0002172658203751343</v>
+        <v>0.000262083059170054</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.001361730670937256</v>
+        <v>0.001321132363706953</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.002175996208552469</v>
+        <v>0.001431042693054507</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.001018441919360671</v>
+        <v>0.0008347096804887822</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.0006340849198866599</v>
+        <v>0.0003991214696885848</v>
       </c>
       <c r="CU8" t="n">
-        <v>0.0001341838016208907</v>
+        <v>7.396020435690431e-05</v>
       </c>
       <c r="CV8" t="n">
-        <v>0.0003712467169345396</v>
+        <v>5.913674490794496e-05</v>
       </c>
       <c r="CW8" t="n">
         <v>0</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.001127947842917526</v>
+        <v>-0.0001109008940877759</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.001218553907349357</v>
+        <v>-0.000162255159963115</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.000258560146050954</v>
+        <v>0.0002966633166700012</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.0004713449867186165</v>
+        <v>0.0002817352430856679</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.004034263606864946</v>
+        <v>0.001850557434792422</v>
       </c>
       <c r="DC8" t="n">
-        <v>-3.21731129085484e-05</v>
+        <v>0.00110315423852905</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.352351369485141e-05</v>
+        <v>0.0001558937232560703</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.001121436187700603</v>
+        <v>0.001059669973005786</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.0008026604293401851</v>
+        <v>-0.0002416930908329229</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.0003735362027541517</v>
+        <v>-6.654840501962023e-05</v>
       </c>
       <c r="DH8" t="n">
-        <v>6.109736834260804e-05</v>
+        <v>0.0002010560597684785</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.0002716872525817815</v>
+        <v>-0.000180313334031551</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.0005544266201229581</v>
+        <v>-0.0001656953304931541</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.0005024299206001281</v>
+        <v>0.001235690534105555</v>
       </c>
       <c r="DL8" t="n">
-        <v>8.218837187935203e-05</v>
+        <v>0.0002461523748305855</v>
       </c>
       <c r="DM8" t="n">
-        <v>0.0004426027416634032</v>
+        <v>0.001165339254458012</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.00076635740156826</v>
+        <v>0.002043950723546148</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.0006354411479829846</v>
+        <v>0.0003502228726864537</v>
       </c>
       <c r="DP8" t="n">
-        <v>-0.0009660455383732613</v>
+        <v>-0.0001271133935278945</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.0002139321493126317</v>
+        <v>9.618240321653259e-05</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.0005921903825971964</v>
+        <v>-7.400828892836775e-06</v>
       </c>
       <c r="DS8" t="n">
-        <v>2.23081499107658e-05</v>
+        <v>2.969367428299619e-05</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.0008798139088617707</v>
+        <v>0.0002242126527764093</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.001343115793597252</v>
+        <v>-0.0003140057655481976</v>
       </c>
       <c r="DV8" t="n">
         <v>0</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.0003016237867136978</v>
+        <v>0.000174371116429134</v>
       </c>
       <c r="DX8" t="n">
-        <v>-0.0006351047272827898</v>
+        <v>0.0001421989463848083</v>
       </c>
       <c r="DY8" t="n">
-        <v>-0.001208730111108411</v>
+        <v>0.001642985364909413</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.0004846997723700897</v>
+        <v>0.0002655024746634787</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.0005142535621690952</v>
+        <v>0.0002722823963523441</v>
       </c>
       <c r="EB8" t="n">
-        <v>-0.0006082408068201317</v>
+        <v>-0.000833101515371204</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.0006359471177668607</v>
+        <v>0.000683035508311769</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.000646791068446509</v>
+        <v>-0.0001664725981548487</v>
       </c>
       <c r="EE8" t="n">
-        <v>0.0001322542410624156</v>
+        <v>0</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.000465826634393704</v>
+        <v>0.0003463490109174683</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.0001473294982512558</v>
+        <v>0.0002366515225895593</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.0002550002562398679</v>
+        <v>8.821506591276118e-05</v>
       </c>
       <c r="EI8" t="n">
-        <v>-7.436049970263591e-06</v>
+        <v>0.00032698166186442</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.0003541135514521954</v>
+        <v>0.0006570313761310203</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.0001856294926409346</v>
+        <v>0.0002360854816254837</v>
       </c>
       <c r="EL8" t="n">
-        <v>0</v>
+        <v>5.437531858824008e-05</v>
       </c>
       <c r="EM8" t="n">
-        <v>0.0001990302514509823</v>
+        <v>2.215657311669117e-05</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.0001323196772153201</v>
+        <v>0.0001395930067531442</v>
       </c>
       <c r="EO8" t="n">
         <v>0</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.0001722228713654961</v>
+        <v>0.0003246450032826836</v>
       </c>
       <c r="EQ8" t="n">
-        <v>1.198449358910668e-06</v>
+        <v>-4.431314623338234e-05</v>
       </c>
       <c r="ER8" t="n">
-        <v>0</v>
+        <v>2.292176039120075e-05</v>
       </c>
       <c r="ES8" t="n">
-        <v>8.500008541328929e-05</v>
+        <v>2.931990479994318e-05</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.0006490043944445967</v>
+        <v>0.000515333932066142</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.0007022601151143365</v>
+        <v>-5.460218408734064e-05</v>
       </c>
       <c r="EV8" t="n">
-        <v>4.68018720748753e-05</v>
+        <v>-1.110223024625157e-17</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.0004866213327746505</v>
+        <v>-1.480165778568743e-05</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.0003882313792249569</v>
+        <v>8.878366380586089e-05</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.0004695587384761474</v>
+        <v>-0.0002393305663682455</v>
       </c>
     </row>
     <row r="9">
@@ -4490,466 +4490,466 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.004217045119433838</v>
+        <v>0.001665675193337279</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00275775618928239</v>
+        <v>0.001123595505617936</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001405867970660102</v>
+        <v>0.0009219245174301172</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003480071386079741</v>
+        <v>0.003966844286560056</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001466992665036637</v>
+        <v>0.0009168704156479523</v>
       </c>
       <c r="G9" t="n">
-        <v>0.008229721728833583</v>
+        <v>0.01737714624037888</v>
       </c>
       <c r="H9" t="n">
-        <v>0.002308892355694225</v>
+        <v>0.002498512790005914</v>
       </c>
       <c r="I9" t="n">
-        <v>0.002215288611544475</v>
+        <v>0.003276131045241804</v>
       </c>
       <c r="J9" t="n">
-        <v>0.004705534181710591</v>
+        <v>0.006542332741266965</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0008286475288546757</v>
+        <v>0.0006543723973824634</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0008461297398934641</v>
+        <v>0.0005640864932622725</v>
       </c>
       <c r="M9" t="n">
-        <v>0.004512691946098412</v>
+        <v>0.00203697900344717</v>
       </c>
       <c r="N9" t="n">
-        <v>0.01680547293277813</v>
+        <v>0.007674003569303933</v>
       </c>
       <c r="O9" t="n">
-        <v>0.003509815585960763</v>
+        <v>0.003697900344719496</v>
       </c>
       <c r="P9" t="n">
-        <v>0.003242117787031529</v>
+        <v>0.001538916839301596</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0276621058893516</v>
+        <v>0.0138839550029603</v>
       </c>
       <c r="R9" t="n">
-        <v>0.002799882110226926</v>
+        <v>0.001803178484107593</v>
       </c>
       <c r="S9" t="n">
-        <v>0.006267627702914469</v>
+        <v>0.003420582986317611</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0008923259964307206</v>
+        <v>0.001210025929127023</v>
       </c>
       <c r="U9" t="n">
-        <v>0.004521118381915534</v>
+        <v>0.002367564368156316</v>
       </c>
       <c r="V9" t="n">
-        <v>0.006048260733312461</v>
+        <v>0.003777513384889897</v>
       </c>
       <c r="W9" t="n">
-        <v>0.003086797066014624</v>
+        <v>0.003242117787031462</v>
       </c>
       <c r="X9" t="n">
-        <v>0.01231588843622691</v>
+        <v>0.01360075211532433</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.001372854914196553</v>
+        <v>0.0007073386383730674</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.01612135633551459</v>
+        <v>0.01770278271166366</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.007282415630550587</v>
+        <v>0.01678507992895201</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.001833740831295805</v>
+        <v>0.002261613691931552</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.004400977995109967</v>
+        <v>0.002151488358384868</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.01243307555026771</v>
+        <v>0.009470257472625065</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.02278405710886381</v>
+        <v>0.0183819155264723</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.001894051494525006</v>
+        <v>0.005502736963411081</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.0009431181844974712</v>
+        <v>0.001738874152667214</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.003415857098088404</v>
+        <v>0.0009401441554371615</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.001503094606542854</v>
+        <v>0.001945181255526041</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.007079119571683545</v>
+        <v>0.009577632361689426</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.0406157489638839</v>
+        <v>0.03218390804597696</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.001535568787214048</v>
+        <v>0.002397868561278815</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.02501487209994053</v>
+        <v>0.01151100535395591</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.003259166405515534</v>
+        <v>0.0009048361934477223</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.005202130993418996</v>
+        <v>0.00576621748668128</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.001974302726418064</v>
+        <v>0.00153937240970986</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.02834622248661512</v>
+        <v>0.003625110521662212</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.01525877453896493</v>
+        <v>0.01954193932183219</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.005239786856127859</v>
+        <v>0.001414677276746201</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.004261615862681289</v>
+        <v>0.01204854943753697</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.004527966854098875</v>
+        <v>0.004745063365752966</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.00176834659593279</v>
+        <v>0.002858826996757979</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.006267627702914469</v>
+        <v>0.0002082093991671252</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.001191931540342239</v>
+        <v>0.001901469317199622</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.01267102914931592</v>
+        <v>0.009325044404973315</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.001786228752520869</v>
+        <v>0.00239124171708438</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.01088637715645451</v>
+        <v>0.01502082093991666</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.03307555026769782</v>
+        <v>0.009637120761451456</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.001037165082108915</v>
+        <v>0.001061633736361034</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.0005195599022004505</v>
+        <v>0.001070791195716769</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.002711464780430295</v>
+        <v>0.002766210588935114</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.01287923854848305</v>
+        <v>0.008837355061109354</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.002368265245707468</v>
+        <v>0.002363367799113725</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.002825698988697201</v>
+        <v>0.001095322676139709</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.03179654967281381</v>
+        <v>0.02117787031528847</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.0039559785841761</v>
+        <v>0.005506216696269928</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.005294467578822138</v>
+        <v>0.00439139404656641</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.001473622163277322</v>
+        <v>0.001211225997045784</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.00350987151363209</v>
+        <v>0.01121965660153934</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.01745984533016064</v>
+        <v>0.008655562165377695</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.003478533375117532</v>
+        <v>0.003566165635131113</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.001441554371670339</v>
+        <v>0.002947244326554632</v>
       </c>
       <c r="BQ9" t="n">
         <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.01190849263553747</v>
+        <v>0.0187388987566607</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.005859607376561593</v>
+        <v>0.003448275862068917</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.001657295057709351</v>
+        <v>0.002948982601002714</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.009213412723284242</v>
+        <v>0.005772646536412041</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.006573468173706154</v>
+        <v>0.004745063365752989</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.0005651397977394779</v>
+        <v>0.0004143237644273379</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.003885929175806957</v>
+        <v>0.005654233274126652</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.008060678167757296</v>
+        <v>0.005934889080956463</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.007168352171326609</v>
+        <v>0.001665675193337246</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.002930728241563019</v>
+        <v>0.00106084243369734</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.003551346552234414</v>
+        <v>0.005713439905269346</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.005651397977394423</v>
+        <v>0.003420582986317611</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.002564102564102566</v>
+        <v>0.002210433244915944</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.00440214158239145</v>
+        <v>0.002261613691931563</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.006811421772754333</v>
+        <v>0.003019538188277049</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.001487209994051164</v>
+        <v>0.001033973412112255</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.001238836070296756</v>
+        <v>0.002632403635224045</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.001595273264401764</v>
+        <v>0.0006192863462106124</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.0002947244326554355</v>
+        <v>0.0002654084340902862</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.0008557457212713393</v>
+        <v>0.003718024985127843</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.00231902225007834</v>
+        <v>0.002078239608801968</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.00256723716381414</v>
+        <v>0.003878034339846026</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.003789731051344703</v>
+        <v>0.002320047590719754</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.004278728606356919</v>
+        <v>0.001487209994051109</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.0003831417624520883</v>
+        <v>0.0009431181844974379</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.003667481662591632</v>
+        <v>0.007312018946121934</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.005324211778703169</v>
+        <v>0.003866745984532971</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.001723597618301476</v>
+        <v>0.00253667481662595</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.001161369193154005</v>
+        <v>0.002569727358194929</v>
       </c>
       <c r="CU9" t="n">
-        <v>0.0002948982601003181</v>
+        <v>0.000738552437223039</v>
       </c>
       <c r="CV9" t="n">
-        <v>0.0008547008547008406</v>
+        <v>0.0003361858190709443</v>
       </c>
       <c r="CW9" t="n">
         <v>0</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.002108801955990181</v>
+        <v>0.001711491442542823</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.01135119562085853</v>
+        <v>0.004263900893114336</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.001041046995835848</v>
+        <v>0.0006552262090483319</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.0008625817965496995</v>
+        <v>0.000917702782711638</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.005264723378941127</v>
+        <v>0.002349791790600786</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.0004584352078239262</v>
+        <v>0.003178484107579494</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.001797819039198356</v>
+        <v>0.0006050129645635005</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.002944675788221307</v>
+        <v>0.004174067495559453</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.003226735811005477</v>
+        <v>0.001864456939923098</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.0006794682422451958</v>
+        <v>0.002634695085849581</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.003697900344719518</v>
+        <v>0.002593575007368054</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.001805267830719126</v>
+        <v>0.002269378131447042</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.0008862629246676468</v>
+        <v>0.001011302795954749</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.001436430317848381</v>
+        <v>0.00161980440097802</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.0001772525849335294</v>
+        <v>0.0002820432466311251</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.006097560975609773</v>
+        <v>0.002416740347774782</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.001060842433697329</v>
+        <v>0.003881418092909572</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.001864456939923032</v>
+        <v>0.003507220748600026</v>
       </c>
       <c r="DP9" t="n">
-        <v>-5.908419497784312e-05</v>
+        <v>0.001213376738680105</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.0003569303985722971</v>
+        <v>0.0005599764220453496</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.001208370173887397</v>
+        <v>0.0001528117359413383</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.0002193669696019862</v>
+        <v>9.401441554370837e-05</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.001650456822870605</v>
+        <v>0.004067197170645398</v>
       </c>
       <c r="DU9" t="n">
-        <v>0.003018644569399265</v>
+        <v>0.004833480695549619</v>
       </c>
       <c r="DV9" t="n">
-        <v>3.056234718825657e-05</v>
+        <v>0</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.001477104874446078</v>
+        <v>0.0004387339392039946</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.004134443783462216</v>
+        <v>0.002122015915119324</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.003331295843520732</v>
+        <v>0.002505157677571412</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.001219512195121986</v>
+        <v>0.0004368174726989027</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.0009795447997695162</v>
+        <v>0.001120613388381075</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.002839313572542912</v>
+        <v>0.00195908959953901</v>
       </c>
       <c r="EC9" t="n">
-        <v>0.004491374182034502</v>
+        <v>0.002231051344743307</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.001558679706601418</v>
+        <v>0.001124925991711023</v>
       </c>
       <c r="EE9" t="n">
-        <v>0.0003569303985722971</v>
+        <v>0.0002071618822136689</v>
       </c>
       <c r="EF9" t="n">
-        <v>0.001477104874446078</v>
+        <v>0.0008625817965496107</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.0005897965202005917</v>
+        <v>0.002338661930136121</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.000531757754800588</v>
+        <v>0.0002959455460195271</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.0007778738115816752</v>
+        <v>0.0008552049542908336</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.0008584961515689105</v>
+        <v>0.001805802249851951</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.001388478581979313</v>
+        <v>0.001031535514294091</v>
       </c>
       <c r="EL9" t="n">
-        <v>0.0001728608470181414</v>
+        <v>0.0001179593040401272</v>
       </c>
       <c r="EM9" t="n">
-        <v>0.0004461629982153825</v>
+        <v>0.000621669626998178</v>
       </c>
       <c r="EN9" t="n">
-        <v>0.0002063071028588048</v>
+        <v>0.001776198934280604</v>
       </c>
       <c r="EO9" t="n">
         <v>0</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.0008030933967876575</v>
+        <v>0.0005948839976204323</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.001249256395003007</v>
+        <v>0.0006487761722206442</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.0001479727730097635</v>
+        <v>8.880994671401909e-05</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.0002881014116968839</v>
+        <v>0.0002363367799113725</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.001268062518431223</v>
+        <v>0.001242971293282036</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.002230814991076746</v>
+        <v>0.0002663509914175743</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.0002139364303178182</v>
+        <v>0.00014801657785668</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.001657785671995215</v>
+        <v>0.001297552344441244</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.00157644259369425</v>
+        <v>0.002013025458851336</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.001272942569567748</v>
+        <v>0.002101835405565378</v>
       </c>
     </row>
   </sheetData>
